--- a/Team-Data/2007-08/1-20-2007-08.xlsx
+++ b/Team-Data/2007-08/1-20-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -757,7 +824,7 @@
         <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>27</v>
@@ -2813,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3511,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
+        <v>0.462</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3773,7 +3840,7 @@
         <v>33.6</v>
       </c>
       <c r="J19" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.434</v>
@@ -3782,46 +3849,46 @@
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="O19" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P19" t="n">
         <v>28.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R19" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S19" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
         <v>41.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V19" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W19" t="n">
         <v>6.7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA19" t="n">
         <v>23.4</v>
@@ -3830,10 +3897,10 @@
         <v>93.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
@@ -3845,13 +3912,13 @@
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
@@ -3872,10 +3939,10 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>18</v>
@@ -3905,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4485,7 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
         <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>0.707</v>
+        <v>0.7</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="J24" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.49</v>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M24" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O24" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P24" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R24" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>27.6</v>
       </c>
       <c r="V24" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W24" t="n">
         <v>7.2</v>
@@ -4728,31 +4795,31 @@
         <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z24" t="n">
         <v>19.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>110</v>
+        <v>109.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE24" t="n">
         <v>3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2</v>
       </c>
       <c r="AF24" t="n">
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
@@ -4773,7 +4840,7 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="n">
         <v>24</v>
@@ -4782,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4800,13 +4867,13 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>3</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4988,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5386,7 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO27" t="n">
         <v>25</v>
@@ -5364,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-20-2007-08</t>
+          <t>2008-01-20</t>
         </is>
       </c>
     </row>
